--- a/Excel/Timeline_elezioni_items.xlsx
+++ b/Excel/Timeline_elezioni_items.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="RVfKiftxlpJW0qdbokQiu/nSjK1ZiirECJ6cw+/z/JU="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="sQtA4dcghXXd0ZJ+AHOleFT1Sto2/IYXz8mLrwCBDsQ="/>
     </ext>
   </extLst>
 </workbook>
@@ -175,7 +175,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjaNQen4O93rDCiETy0l8+kFULuSQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhrmem7iCxOe1cCq86Hgwe3jaOBXQ=="/>
     </ext>
   </extLst>
 </comments>
@@ -270,9 +270,10 @@
     <r>
       <rPr>
         <rFont val="Arial"/>
-        <color rgb="FF1F1F1F"/>
+        <color rgb="FF1155CC"/>
+        <u/>
       </rPr>
-      <t>Lista_1948.html</t>
+      <t>https://vegnachristian14.github.io/Prima-Repubblica-prime-elezioni/Lista_1948.html</t>
     </r>
     <r>
       <rPr>
@@ -308,7 +309,30 @@
     <t>Elezioni politiche del 1953</t>
   </si>
   <si>
-    <t>&lt;a href="Lista_1953.html"&gt;Visualizza tutte le risorse relative alle elezioni politiche del 1953&lt;/a&gt;</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>&lt;a href="</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://vegnachristian14.github.io/Prima-Repubblica-prime-elezioni/Lista_1953.html</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>"&gt;Visualizza tutte le risorse relative alle elezioni politiche del 1953&lt;/a&gt;</t>
+    </r>
   </si>
   <si>
     <t>https://commons.wikimedia.org/wiki/File:Camera_1953_Partiti.svg</t>
@@ -332,7 +356,30 @@
     <t>Elezioni politiche del 1958</t>
   </si>
   <si>
-    <t>&lt;a href="Lista_1958.html"&gt;Visualizza tutte le risorse relative alle elezioni politiche del 1958&lt;/a&gt;</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>&lt;a href="</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://vegnachristian14.github.io/Prima-Repubblica-prime-elezioni/Lista_1958.html</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>"&gt;Visualizza tutte le risorse relative alle elezioni politiche del 1958&lt;/a&gt;</t>
+    </r>
   </si>
   <si>
     <t>https://commons.wikimedia.org/wiki/File:Elezioni_Camera_1958_Comuni.png</t>
@@ -351,7 +398,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.###############"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -363,13 +410,16 @@
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF202122"/>
@@ -378,22 +428,15 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
@@ -402,12 +445,6 @@
     <font>
       <u/>
       <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -497,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
@@ -534,109 +571,106 @@
     <xf borderId="0" fillId="6" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="0" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="0" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="7" fontId="0" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="0" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="7" fontId="0" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="7" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="7" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="7" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="0" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="9" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf borderId="0" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="9" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="9" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="10" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="10" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="10" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="10" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="10" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1021,10 +1055,10 @@
       <c r="J4" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="K4" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="41" t="s">
+      <c r="L4" s="40" t="s">
         <v>35</v>
       </c>
       <c r="M4" s="24" t="s">
@@ -1040,8 +1074,8 @@
       <c r="Q4" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="42"/>
-      <c r="S4" s="43"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="42"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="24">
@@ -1068,7 +1102,7 @@
       <c r="J5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="31" t="s">
         <v>42</v>
       </c>
       <c r="L5" s="32" t="s">
@@ -1101,15 +1135,15 @@
       <c r="H6" s="37"/>
       <c r="I6" s="38"/>
       <c r="J6" s="39"/>
-      <c r="K6" s="44"/>
+      <c r="K6" s="43"/>
       <c r="L6" s="39"/>
       <c r="M6" s="33"/>
-      <c r="N6" s="45"/>
+      <c r="N6" s="44"/>
       <c r="O6" s="33"/>
       <c r="P6" s="33"/>
       <c r="Q6" s="39"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="24"/>
@@ -1122,7 +1156,7 @@
       <c r="H7" s="28"/>
       <c r="I7" s="29"/>
       <c r="J7" s="30"/>
-      <c r="K7" s="46"/>
+      <c r="K7" s="45"/>
       <c r="L7" s="30"/>
       <c r="M7" s="24"/>
       <c r="N7" s="24"/>
@@ -1143,15 +1177,15 @@
       <c r="H8" s="37"/>
       <c r="I8" s="38"/>
       <c r="J8" s="39"/>
-      <c r="K8" s="44"/>
+      <c r="K8" s="43"/>
       <c r="L8" s="39"/>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
       <c r="O8" s="33"/>
       <c r="P8" s="33"/>
       <c r="Q8" s="39"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="33"/>
@@ -1164,15 +1198,15 @@
       <c r="H9" s="37"/>
       <c r="I9" s="38"/>
       <c r="J9" s="38"/>
-      <c r="K9" s="44"/>
+      <c r="K9" s="43"/>
       <c r="L9" s="39"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
       <c r="O9" s="33"/>
       <c r="P9" s="33"/>
       <c r="Q9" s="39"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
     </row>
     <row r="10" ht="12.75" customHeight="1"/>
     <row r="11" ht="12.75" customHeight="1"/>
@@ -2167,11 +2201,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId2" ref="L3"/>
-    <hyperlink r:id="rId3" ref="L4"/>
-    <hyperlink r:id="rId4" ref="L5"/>
+    <hyperlink r:id="rId2" ref="K3"/>
+    <hyperlink r:id="rId3" ref="L3"/>
+    <hyperlink r:id="rId4" ref="K4"/>
+    <hyperlink r:id="rId5" ref="L4"/>
+    <hyperlink r:id="rId6" ref="K5"/>
+    <hyperlink r:id="rId7" ref="L5"/>
   </hyperlinks>
-  <drawing r:id="rId5"/>
-  <legacyDrawing r:id="rId6"/>
+  <drawing r:id="rId8"/>
+  <legacyDrawing r:id="rId9"/>
 </worksheet>
 </file>